--- a/Tomoscan_pso_interlaced/risultati_multiturns_N32_K4_PSO20000.xlsx
+++ b/Tomoscan_pso_interlaced/risultati_multiturns_N32_K4_PSO20000.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="MOD360" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UNWRAPPED" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="COUNTS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DELTA_THETA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UNWRAPPED_ACQ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="COUNTS_PSO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DELTA_THETA_PSO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_mod360</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_unwrapped_acq</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -4078,7 +4078,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>theta_unwrapped_deg</t>
+          <t>theta_monotonic_deg</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -4113,1766 +4113,1766 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="B3" t="n">
-        <v>645</v>
+        <v>161</v>
       </c>
       <c r="C3" t="n">
-        <v>645</v>
+        <v>161</v>
       </c>
       <c r="D3" t="n">
-        <v>645</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23.2258064516129</v>
+        <v>5.806451612903226</v>
       </c>
       <c r="B4" t="n">
-        <v>1290</v>
+        <v>323</v>
       </c>
       <c r="C4" t="n">
-        <v>1290</v>
+        <v>323</v>
       </c>
       <c r="D4" t="n">
-        <v>1290</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34.83870967741936</v>
+        <v>8.70967741935484</v>
       </c>
       <c r="B5" t="n">
-        <v>1935</v>
+        <v>484</v>
       </c>
       <c r="C5" t="n">
-        <v>1935</v>
+        <v>484</v>
       </c>
       <c r="D5" t="n">
-        <v>1935</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46.45161290322581</v>
+        <v>11.61290322580645</v>
       </c>
       <c r="B6" t="n">
-        <v>2581</v>
+        <v>645</v>
       </c>
       <c r="C6" t="n">
-        <v>2581</v>
+        <v>645</v>
       </c>
       <c r="D6" t="n">
-        <v>2581</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58.06451612903226</v>
+        <v>14.51612903225806</v>
       </c>
       <c r="B7" t="n">
-        <v>3226</v>
+        <v>806</v>
       </c>
       <c r="C7" t="n">
-        <v>3226</v>
+        <v>806</v>
       </c>
       <c r="D7" t="n">
-        <v>3226</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69.67741935483872</v>
+        <v>17.41935483870968</v>
       </c>
       <c r="B8" t="n">
-        <v>3871</v>
+        <v>968</v>
       </c>
       <c r="C8" t="n">
-        <v>3871</v>
+        <v>968</v>
       </c>
       <c r="D8" t="n">
-        <v>3871</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81.29032258064517</v>
+        <v>20.32258064516129</v>
       </c>
       <c r="B9" t="n">
-        <v>4516</v>
+        <v>1129</v>
       </c>
       <c r="C9" t="n">
-        <v>4516</v>
+        <v>1129</v>
       </c>
       <c r="D9" t="n">
-        <v>4516</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92.90322580645162</v>
+        <v>23.2258064516129</v>
       </c>
       <c r="B10" t="n">
-        <v>5161</v>
+        <v>1290</v>
       </c>
       <c r="C10" t="n">
-        <v>5161</v>
+        <v>1290</v>
       </c>
       <c r="D10" t="n">
-        <v>5161</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104.5161290322581</v>
+        <v>26.12903225806452</v>
       </c>
       <c r="B11" t="n">
-        <v>5806</v>
+        <v>1452</v>
       </c>
       <c r="C11" t="n">
-        <v>5806</v>
+        <v>1452</v>
       </c>
       <c r="D11" t="n">
-        <v>5806</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116.1290322580645</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="B12" t="n">
-        <v>6452</v>
+        <v>1613</v>
       </c>
       <c r="C12" t="n">
-        <v>6452</v>
+        <v>1613</v>
       </c>
       <c r="D12" t="n">
-        <v>6452</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127.741935483871</v>
+        <v>31.93548387096774</v>
       </c>
       <c r="B13" t="n">
-        <v>7097</v>
+        <v>1774</v>
       </c>
       <c r="C13" t="n">
-        <v>7097</v>
+        <v>1774</v>
       </c>
       <c r="D13" t="n">
-        <v>7097</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>139.3548387096774</v>
+        <v>34.83870967741936</v>
       </c>
       <c r="B14" t="n">
-        <v>7742</v>
+        <v>1935</v>
       </c>
       <c r="C14" t="n">
-        <v>7742</v>
+        <v>1935</v>
       </c>
       <c r="D14" t="n">
-        <v>7742</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>150.9677419354839</v>
+        <v>37.74193548387097</v>
       </c>
       <c r="B15" t="n">
-        <v>8387</v>
+        <v>2097</v>
       </c>
       <c r="C15" t="n">
-        <v>8387</v>
+        <v>2097</v>
       </c>
       <c r="D15" t="n">
-        <v>8387</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>162.5806451612903</v>
+        <v>40.64516129032258</v>
       </c>
       <c r="B16" t="n">
-        <v>9032</v>
+        <v>2258</v>
       </c>
       <c r="C16" t="n">
-        <v>9032</v>
+        <v>2258</v>
       </c>
       <c r="D16" t="n">
-        <v>9032</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>174.1935483870968</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="B17" t="n">
-        <v>9677</v>
+        <v>2419</v>
       </c>
       <c r="C17" t="n">
-        <v>9677</v>
+        <v>2419</v>
       </c>
       <c r="D17" t="n">
-        <v>9677</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>185.8064516129032</v>
+        <v>46.45161290322581</v>
       </c>
       <c r="B18" t="n">
-        <v>10323</v>
+        <v>2581</v>
       </c>
       <c r="C18" t="n">
-        <v>10323</v>
+        <v>2581</v>
       </c>
       <c r="D18" t="n">
-        <v>10323</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>197.4193548387097</v>
+        <v>49.35483870967742</v>
       </c>
       <c r="B19" t="n">
-        <v>10968</v>
+        <v>2742</v>
       </c>
       <c r="C19" t="n">
-        <v>10968</v>
+        <v>2742</v>
       </c>
       <c r="D19" t="n">
-        <v>10968</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>209.0322580645161</v>
+        <v>52.25806451612903</v>
       </c>
       <c r="B20" t="n">
-        <v>11613</v>
+        <v>2903</v>
       </c>
       <c r="C20" t="n">
-        <v>11613</v>
+        <v>2903</v>
       </c>
       <c r="D20" t="n">
-        <v>11613</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>220.6451612903226</v>
+        <v>55.16129032258065</v>
       </c>
       <c r="B21" t="n">
-        <v>12258</v>
+        <v>3065</v>
       </c>
       <c r="C21" t="n">
-        <v>12258</v>
+        <v>3065</v>
       </c>
       <c r="D21" t="n">
-        <v>12258</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>232.258064516129</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="B22" t="n">
-        <v>12903</v>
+        <v>3226</v>
       </c>
       <c r="C22" t="n">
-        <v>12903</v>
+        <v>3226</v>
       </c>
       <c r="D22" t="n">
-        <v>12903</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>243.8709677419355</v>
+        <v>60.96774193548387</v>
       </c>
       <c r="B23" t="n">
-        <v>13548</v>
+        <v>3387</v>
       </c>
       <c r="C23" t="n">
-        <v>13548</v>
+        <v>3387</v>
       </c>
       <c r="D23" t="n">
-        <v>13548</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>255.483870967742</v>
+        <v>63.87096774193549</v>
       </c>
       <c r="B24" t="n">
-        <v>14194</v>
+        <v>3548</v>
       </c>
       <c r="C24" t="n">
-        <v>14194</v>
+        <v>3548</v>
       </c>
       <c r="D24" t="n">
-        <v>14194</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>267.0967741935484</v>
+        <v>66.7741935483871</v>
       </c>
       <c r="B25" t="n">
-        <v>14839</v>
+        <v>3710</v>
       </c>
       <c r="C25" t="n">
-        <v>14839</v>
+        <v>3710</v>
       </c>
       <c r="D25" t="n">
-        <v>14839</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>278.7096774193549</v>
+        <v>69.67741935483872</v>
       </c>
       <c r="B26" t="n">
-        <v>15484</v>
+        <v>3871</v>
       </c>
       <c r="C26" t="n">
-        <v>15484</v>
+        <v>3871</v>
       </c>
       <c r="D26" t="n">
-        <v>15484</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>290.3225806451613</v>
+        <v>72.58064516129032</v>
       </c>
       <c r="B27" t="n">
-        <v>16129</v>
+        <v>4032</v>
       </c>
       <c r="C27" t="n">
-        <v>16129</v>
+        <v>4032</v>
       </c>
       <c r="D27" t="n">
-        <v>16129</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>301.9354838709677</v>
+        <v>75.48387096774194</v>
       </c>
       <c r="B28" t="n">
-        <v>16774</v>
+        <v>4194</v>
       </c>
       <c r="C28" t="n">
-        <v>16774</v>
+        <v>4194</v>
       </c>
       <c r="D28" t="n">
-        <v>16774</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>313.5483870967742</v>
+        <v>78.38709677419355</v>
       </c>
       <c r="B29" t="n">
-        <v>17419</v>
+        <v>4355</v>
       </c>
       <c r="C29" t="n">
-        <v>17419</v>
+        <v>4355</v>
       </c>
       <c r="D29" t="n">
-        <v>17419</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>325.1612903225807</v>
+        <v>81.29032258064517</v>
       </c>
       <c r="B30" t="n">
-        <v>18065</v>
+        <v>4516</v>
       </c>
       <c r="C30" t="n">
-        <v>18065</v>
+        <v>4516</v>
       </c>
       <c r="D30" t="n">
-        <v>18065</v>
+        <v>4516</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>336.7741935483871</v>
+        <v>84.19354838709678</v>
       </c>
       <c r="B31" t="n">
-        <v>18710</v>
+        <v>4677</v>
       </c>
       <c r="C31" t="n">
-        <v>18710</v>
+        <v>4677</v>
       </c>
       <c r="D31" t="n">
-        <v>18710</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>348.3870967741935</v>
+        <v>87.09677419354838</v>
       </c>
       <c r="B32" t="n">
-        <v>19355</v>
+        <v>4839</v>
       </c>
       <c r="C32" t="n">
-        <v>19355</v>
+        <v>4839</v>
       </c>
       <c r="D32" t="n">
-        <v>19355</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="B33" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="C33" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="D33" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2.903225806451613</v>
+        <v>92.90322580645162</v>
       </c>
       <c r="B34" t="n">
-        <v>161</v>
+        <v>5161</v>
       </c>
       <c r="C34" t="n">
-        <v>161</v>
+        <v>5161</v>
       </c>
       <c r="D34" t="n">
-        <v>161</v>
+        <v>5161</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>14.51612903225806</v>
+        <v>95.80645161290323</v>
       </c>
       <c r="B35" t="n">
-        <v>806</v>
+        <v>5323</v>
       </c>
       <c r="C35" t="n">
-        <v>806</v>
+        <v>5323</v>
       </c>
       <c r="D35" t="n">
-        <v>806</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26.12903225806452</v>
+        <v>98.70967741935485</v>
       </c>
       <c r="B36" t="n">
-        <v>1452</v>
+        <v>5484</v>
       </c>
       <c r="C36" t="n">
-        <v>1452</v>
+        <v>5484</v>
       </c>
       <c r="D36" t="n">
-        <v>1452</v>
+        <v>5484</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37.74193548387097</v>
+        <v>101.6129032258064</v>
       </c>
       <c r="B37" t="n">
-        <v>2097</v>
+        <v>5645</v>
       </c>
       <c r="C37" t="n">
-        <v>2097</v>
+        <v>5645</v>
       </c>
       <c r="D37" t="n">
-        <v>2097</v>
+        <v>5645</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>49.35483870967742</v>
+        <v>104.5161290322581</v>
       </c>
       <c r="B38" t="n">
-        <v>2742</v>
+        <v>5806</v>
       </c>
       <c r="C38" t="n">
-        <v>2742</v>
+        <v>5806</v>
       </c>
       <c r="D38" t="n">
-        <v>2742</v>
+        <v>5806</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>60.96774193548387</v>
+        <v>107.4193548387097</v>
       </c>
       <c r="B39" t="n">
-        <v>3387</v>
+        <v>5968</v>
       </c>
       <c r="C39" t="n">
-        <v>3387</v>
+        <v>5968</v>
       </c>
       <c r="D39" t="n">
-        <v>3387</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>72.58064516129032</v>
+        <v>110.3225806451613</v>
       </c>
       <c r="B40" t="n">
-        <v>4032</v>
+        <v>6129</v>
       </c>
       <c r="C40" t="n">
-        <v>4032</v>
+        <v>6129</v>
       </c>
       <c r="D40" t="n">
-        <v>4032</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>84.19354838709678</v>
+        <v>113.2258064516129</v>
       </c>
       <c r="B41" t="n">
-        <v>4677</v>
+        <v>6290</v>
       </c>
       <c r="C41" t="n">
-        <v>4677</v>
+        <v>6290</v>
       </c>
       <c r="D41" t="n">
-        <v>4677</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95.80645161290323</v>
+        <v>116.1290322580645</v>
       </c>
       <c r="B42" t="n">
-        <v>5323</v>
+        <v>6452</v>
       </c>
       <c r="C42" t="n">
-        <v>5323</v>
+        <v>6452</v>
       </c>
       <c r="D42" t="n">
-        <v>5323</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>107.4193548387097</v>
+        <v>119.0322580645161</v>
       </c>
       <c r="B43" t="n">
-        <v>5968</v>
+        <v>6613</v>
       </c>
       <c r="C43" t="n">
-        <v>5968</v>
+        <v>6613</v>
       </c>
       <c r="D43" t="n">
-        <v>5968</v>
+        <v>6613</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119.0322580645161</v>
+        <v>121.9354838709677</v>
       </c>
       <c r="B44" t="n">
-        <v>6613</v>
+        <v>6774</v>
       </c>
       <c r="C44" t="n">
-        <v>6613</v>
+        <v>6774</v>
       </c>
       <c r="D44" t="n">
-        <v>6613</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130.6451612903226</v>
+        <v>124.8387096774194</v>
       </c>
       <c r="B45" t="n">
-        <v>7258</v>
+        <v>6935</v>
       </c>
       <c r="C45" t="n">
-        <v>7258</v>
+        <v>6935</v>
       </c>
       <c r="D45" t="n">
-        <v>7258</v>
+        <v>6935</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>142.258064516129</v>
+        <v>127.741935483871</v>
       </c>
       <c r="B46" t="n">
-        <v>7903</v>
+        <v>7097</v>
       </c>
       <c r="C46" t="n">
-        <v>7903</v>
+        <v>7097</v>
       </c>
       <c r="D46" t="n">
-        <v>7903</v>
+        <v>7097</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>153.8709677419355</v>
+        <v>130.6451612903226</v>
       </c>
       <c r="B47" t="n">
-        <v>8548</v>
+        <v>7258</v>
       </c>
       <c r="C47" t="n">
-        <v>8548</v>
+        <v>7258</v>
       </c>
       <c r="D47" t="n">
-        <v>8548</v>
+        <v>7258</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>165.483870967742</v>
+        <v>133.5483870967742</v>
       </c>
       <c r="B48" t="n">
-        <v>9194</v>
+        <v>7419</v>
       </c>
       <c r="C48" t="n">
-        <v>9194</v>
+        <v>7419</v>
       </c>
       <c r="D48" t="n">
-        <v>9194</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>177.0967741935484</v>
+        <v>136.4516129032258</v>
       </c>
       <c r="B49" t="n">
-        <v>9839</v>
+        <v>7581</v>
       </c>
       <c r="C49" t="n">
-        <v>9839</v>
+        <v>7581</v>
       </c>
       <c r="D49" t="n">
-        <v>9839</v>
+        <v>7581</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>188.7096774193548</v>
+        <v>139.3548387096774</v>
       </c>
       <c r="B50" t="n">
-        <v>10484</v>
+        <v>7742</v>
       </c>
       <c r="C50" t="n">
-        <v>10484</v>
+        <v>7742</v>
       </c>
       <c r="D50" t="n">
-        <v>10484</v>
+        <v>7742</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>200.3225806451613</v>
+        <v>142.258064516129</v>
       </c>
       <c r="B51" t="n">
-        <v>11129</v>
+        <v>7903</v>
       </c>
       <c r="C51" t="n">
-        <v>11129</v>
+        <v>7903</v>
       </c>
       <c r="D51" t="n">
-        <v>11129</v>
+        <v>7903</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>211.9354838709677</v>
+        <v>145.1612903225806</v>
       </c>
       <c r="B52" t="n">
-        <v>11774</v>
+        <v>8065</v>
       </c>
       <c r="C52" t="n">
-        <v>11774</v>
+        <v>8065</v>
       </c>
       <c r="D52" t="n">
-        <v>11774</v>
+        <v>8065</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>223.5483870967742</v>
+        <v>148.0645161290323</v>
       </c>
       <c r="B53" t="n">
-        <v>12419</v>
+        <v>8226</v>
       </c>
       <c r="C53" t="n">
-        <v>12419</v>
+        <v>8226</v>
       </c>
       <c r="D53" t="n">
-        <v>12419</v>
+        <v>8226</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>235.1612903225806</v>
+        <v>150.9677419354839</v>
       </c>
       <c r="B54" t="n">
-        <v>13065</v>
+        <v>8387</v>
       </c>
       <c r="C54" t="n">
-        <v>13065</v>
+        <v>8387</v>
       </c>
       <c r="D54" t="n">
-        <v>13065</v>
+        <v>8387</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>246.7741935483871</v>
+        <v>153.8709677419355</v>
       </c>
       <c r="B55" t="n">
-        <v>13710</v>
+        <v>8548</v>
       </c>
       <c r="C55" t="n">
-        <v>13710</v>
+        <v>8548</v>
       </c>
       <c r="D55" t="n">
-        <v>13710</v>
+        <v>8548</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>258.3870967741935</v>
+        <v>156.7741935483871</v>
       </c>
       <c r="B56" t="n">
-        <v>14355</v>
+        <v>8710</v>
       </c>
       <c r="C56" t="n">
-        <v>14355</v>
+        <v>8710</v>
       </c>
       <c r="D56" t="n">
-        <v>14355</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>270</v>
+        <v>159.6774193548387</v>
       </c>
       <c r="B57" t="n">
-        <v>15000</v>
+        <v>8871</v>
       </c>
       <c r="C57" t="n">
-        <v>15000</v>
+        <v>8871</v>
       </c>
       <c r="D57" t="n">
-        <v>15000</v>
+        <v>8871</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>281.6129032258065</v>
+        <v>162.5806451612903</v>
       </c>
       <c r="B58" t="n">
-        <v>15645</v>
+        <v>9032</v>
       </c>
       <c r="C58" t="n">
-        <v>15645</v>
+        <v>9032</v>
       </c>
       <c r="D58" t="n">
-        <v>15645</v>
+        <v>9032</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>293.2258064516129</v>
+        <v>165.483870967742</v>
       </c>
       <c r="B59" t="n">
-        <v>16290</v>
+        <v>9194</v>
       </c>
       <c r="C59" t="n">
-        <v>16290</v>
+        <v>9194</v>
       </c>
       <c r="D59" t="n">
-        <v>16290</v>
+        <v>9194</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>304.8387096774194</v>
+        <v>168.3870967741936</v>
       </c>
       <c r="B60" t="n">
-        <v>16935</v>
+        <v>9355</v>
       </c>
       <c r="C60" t="n">
-        <v>16935</v>
+        <v>9355</v>
       </c>
       <c r="D60" t="n">
-        <v>16935</v>
+        <v>9355</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>316.4516129032258</v>
+        <v>171.2903225806452</v>
       </c>
       <c r="B61" t="n">
-        <v>17581</v>
+        <v>9516</v>
       </c>
       <c r="C61" t="n">
-        <v>17581</v>
+        <v>9516</v>
       </c>
       <c r="D61" t="n">
-        <v>17581</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>328.0645161290323</v>
+        <v>174.1935483870968</v>
       </c>
       <c r="B62" t="n">
-        <v>18226</v>
+        <v>9677</v>
       </c>
       <c r="C62" t="n">
-        <v>18226</v>
+        <v>9677</v>
       </c>
       <c r="D62" t="n">
-        <v>18226</v>
+        <v>9677</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>339.6774193548387</v>
+        <v>177.0967741935484</v>
       </c>
       <c r="B63" t="n">
-        <v>18871</v>
+        <v>9839</v>
       </c>
       <c r="C63" t="n">
-        <v>18871</v>
+        <v>9839</v>
       </c>
       <c r="D63" t="n">
-        <v>18871</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>351.2903225806452</v>
+        <v>180</v>
       </c>
       <c r="B64" t="n">
-        <v>19516</v>
+        <v>10000</v>
       </c>
       <c r="C64" t="n">
-        <v>19516</v>
+        <v>10000</v>
       </c>
       <c r="D64" t="n">
-        <v>19516</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>362.9032258064516</v>
+        <v>182.9032258064516</v>
       </c>
       <c r="B65" t="n">
-        <v>20161</v>
+        <v>10161</v>
       </c>
       <c r="C65" t="n">
-        <v>20161</v>
+        <v>10161</v>
       </c>
       <c r="D65" t="n">
-        <v>20161</v>
+        <v>10161</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5.806451612903226</v>
+        <v>185.8064516129032</v>
       </c>
       <c r="B66" t="n">
-        <v>323</v>
+        <v>10323</v>
       </c>
       <c r="C66" t="n">
-        <v>323</v>
+        <v>10323</v>
       </c>
       <c r="D66" t="n">
-        <v>323</v>
+        <v>10323</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>17.41935483870968</v>
+        <v>188.7096774193548</v>
       </c>
       <c r="B67" t="n">
-        <v>968</v>
+        <v>10484</v>
       </c>
       <c r="C67" t="n">
-        <v>968</v>
+        <v>10484</v>
       </c>
       <c r="D67" t="n">
-        <v>968</v>
+        <v>10484</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>29.03225806451613</v>
+        <v>191.6129032258065</v>
       </c>
       <c r="B68" t="n">
-        <v>1613</v>
+        <v>10645</v>
       </c>
       <c r="C68" t="n">
-        <v>1613</v>
+        <v>10645</v>
       </c>
       <c r="D68" t="n">
-        <v>1613</v>
+        <v>10645</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>40.64516129032258</v>
+        <v>194.5161290322581</v>
       </c>
       <c r="B69" t="n">
-        <v>2258</v>
+        <v>10806</v>
       </c>
       <c r="C69" t="n">
-        <v>2258</v>
+        <v>10806</v>
       </c>
       <c r="D69" t="n">
-        <v>2258</v>
+        <v>10806</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>52.25806451612903</v>
+        <v>197.4193548387097</v>
       </c>
       <c r="B70" t="n">
-        <v>2903</v>
+        <v>10968</v>
       </c>
       <c r="C70" t="n">
-        <v>2903</v>
+        <v>10968</v>
       </c>
       <c r="D70" t="n">
-        <v>2903</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>63.87096774193549</v>
+        <v>200.3225806451613</v>
       </c>
       <c r="B71" t="n">
-        <v>3548</v>
+        <v>11129</v>
       </c>
       <c r="C71" t="n">
-        <v>3548</v>
+        <v>11129</v>
       </c>
       <c r="D71" t="n">
-        <v>3548</v>
+        <v>11129</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>75.48387096774194</v>
+        <v>203.2258064516129</v>
       </c>
       <c r="B72" t="n">
-        <v>4194</v>
+        <v>11290</v>
       </c>
       <c r="C72" t="n">
-        <v>4194</v>
+        <v>11290</v>
       </c>
       <c r="D72" t="n">
-        <v>4194</v>
+        <v>11290</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87.09677419354838</v>
+        <v>206.1290322580645</v>
       </c>
       <c r="B73" t="n">
-        <v>4839</v>
+        <v>11452</v>
       </c>
       <c r="C73" t="n">
-        <v>4839</v>
+        <v>11452</v>
       </c>
       <c r="D73" t="n">
-        <v>4839</v>
+        <v>11452</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>98.70967741935485</v>
+        <v>209.0322580645161</v>
       </c>
       <c r="B74" t="n">
-        <v>5484</v>
+        <v>11613</v>
       </c>
       <c r="C74" t="n">
-        <v>5484</v>
+        <v>11613</v>
       </c>
       <c r="D74" t="n">
-        <v>5484</v>
+        <v>11613</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>110.3225806451613</v>
+        <v>211.9354838709677</v>
       </c>
       <c r="B75" t="n">
-        <v>6129</v>
+        <v>11774</v>
       </c>
       <c r="C75" t="n">
-        <v>6129</v>
+        <v>11774</v>
       </c>
       <c r="D75" t="n">
-        <v>6129</v>
+        <v>11774</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121.9354838709677</v>
+        <v>214.8387096774194</v>
       </c>
       <c r="B76" t="n">
-        <v>6774</v>
+        <v>11935</v>
       </c>
       <c r="C76" t="n">
-        <v>6774</v>
+        <v>11935</v>
       </c>
       <c r="D76" t="n">
-        <v>6774</v>
+        <v>11935</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133.5483870967742</v>
+        <v>217.741935483871</v>
       </c>
       <c r="B77" t="n">
-        <v>7419</v>
+        <v>12097</v>
       </c>
       <c r="C77" t="n">
-        <v>7419</v>
+        <v>12097</v>
       </c>
       <c r="D77" t="n">
-        <v>7419</v>
+        <v>12097</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>145.1612903225806</v>
+        <v>220.6451612903226</v>
       </c>
       <c r="B78" t="n">
-        <v>8065</v>
+        <v>12258</v>
       </c>
       <c r="C78" t="n">
-        <v>8065</v>
+        <v>12258</v>
       </c>
       <c r="D78" t="n">
-        <v>8065</v>
+        <v>12258</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>156.7741935483871</v>
+        <v>223.5483870967742</v>
       </c>
       <c r="B79" t="n">
-        <v>8710</v>
+        <v>12419</v>
       </c>
       <c r="C79" t="n">
-        <v>8710</v>
+        <v>12419</v>
       </c>
       <c r="D79" t="n">
-        <v>8710</v>
+        <v>12419</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>168.3870967741936</v>
+        <v>226.4516129032258</v>
       </c>
       <c r="B80" t="n">
-        <v>9355</v>
+        <v>12581</v>
       </c>
       <c r="C80" t="n">
-        <v>9355</v>
+        <v>12581</v>
       </c>
       <c r="D80" t="n">
-        <v>9355</v>
+        <v>12581</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>180</v>
+        <v>229.3548387096774</v>
       </c>
       <c r="B81" t="n">
-        <v>10000</v>
+        <v>12742</v>
       </c>
       <c r="C81" t="n">
-        <v>10000</v>
+        <v>12742</v>
       </c>
       <c r="D81" t="n">
-        <v>10000</v>
+        <v>12742</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>191.6129032258065</v>
+        <v>232.258064516129</v>
       </c>
       <c r="B82" t="n">
-        <v>10645</v>
+        <v>12903</v>
       </c>
       <c r="C82" t="n">
-        <v>10645</v>
+        <v>12903</v>
       </c>
       <c r="D82" t="n">
-        <v>10645</v>
+        <v>12903</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>203.2258064516129</v>
+        <v>235.1612903225806</v>
       </c>
       <c r="B83" t="n">
-        <v>11290</v>
+        <v>13065</v>
       </c>
       <c r="C83" t="n">
-        <v>11290</v>
+        <v>13065</v>
       </c>
       <c r="D83" t="n">
-        <v>11290</v>
+        <v>13065</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>214.8387096774194</v>
+        <v>238.0645161290323</v>
       </c>
       <c r="B84" t="n">
-        <v>11935</v>
+        <v>13226</v>
       </c>
       <c r="C84" t="n">
-        <v>11935</v>
+        <v>13226</v>
       </c>
       <c r="D84" t="n">
-        <v>11935</v>
+        <v>13226</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>226.4516129032258</v>
+        <v>240.9677419354839</v>
       </c>
       <c r="B85" t="n">
-        <v>12581</v>
+        <v>13387</v>
       </c>
       <c r="C85" t="n">
-        <v>12581</v>
+        <v>13387</v>
       </c>
       <c r="D85" t="n">
-        <v>12581</v>
+        <v>13387</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>238.0645161290323</v>
+        <v>243.8709677419355</v>
       </c>
       <c r="B86" t="n">
-        <v>13226</v>
+        <v>13548</v>
       </c>
       <c r="C86" t="n">
-        <v>13226</v>
+        <v>13548</v>
       </c>
       <c r="D86" t="n">
-        <v>13226</v>
+        <v>13548</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>249.6774193548387</v>
+        <v>246.7741935483871</v>
       </c>
       <c r="B87" t="n">
-        <v>13871</v>
+        <v>13710</v>
       </c>
       <c r="C87" t="n">
-        <v>13871</v>
+        <v>13710</v>
       </c>
       <c r="D87" t="n">
-        <v>13871</v>
+        <v>13710</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>261.2903225806452</v>
+        <v>249.6774193548387</v>
       </c>
       <c r="B88" t="n">
-        <v>14516</v>
+        <v>13871</v>
       </c>
       <c r="C88" t="n">
-        <v>14516</v>
+        <v>13871</v>
       </c>
       <c r="D88" t="n">
-        <v>14516</v>
+        <v>13871</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>272.9032258064516</v>
+        <v>252.5806451612903</v>
       </c>
       <c r="B89" t="n">
-        <v>15161</v>
+        <v>14032</v>
       </c>
       <c r="C89" t="n">
-        <v>15161</v>
+        <v>14032</v>
       </c>
       <c r="D89" t="n">
-        <v>15161</v>
+        <v>14032</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>284.516129032258</v>
+        <v>255.483870967742</v>
       </c>
       <c r="B90" t="n">
-        <v>15806</v>
+        <v>14194</v>
       </c>
       <c r="C90" t="n">
-        <v>15806</v>
+        <v>14194</v>
       </c>
       <c r="D90" t="n">
-        <v>15806</v>
+        <v>14194</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>296.1290322580645</v>
+        <v>258.3870967741935</v>
       </c>
       <c r="B91" t="n">
-        <v>16452</v>
+        <v>14355</v>
       </c>
       <c r="C91" t="n">
-        <v>16452</v>
+        <v>14355</v>
       </c>
       <c r="D91" t="n">
-        <v>16452</v>
+        <v>14355</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>307.741935483871</v>
+        <v>261.2903225806452</v>
       </c>
       <c r="B92" t="n">
-        <v>17097</v>
+        <v>14516</v>
       </c>
       <c r="C92" t="n">
-        <v>17097</v>
+        <v>14516</v>
       </c>
       <c r="D92" t="n">
-        <v>17097</v>
+        <v>14516</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>319.3548387096774</v>
+        <v>264.1935483870968</v>
       </c>
       <c r="B93" t="n">
-        <v>17742</v>
+        <v>14677</v>
       </c>
       <c r="C93" t="n">
-        <v>17742</v>
+        <v>14677</v>
       </c>
       <c r="D93" t="n">
-        <v>17742</v>
+        <v>14677</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>330.9677419354839</v>
+        <v>267.0967741935484</v>
       </c>
       <c r="B94" t="n">
-        <v>18387</v>
+        <v>14839</v>
       </c>
       <c r="C94" t="n">
-        <v>18387</v>
+        <v>14839</v>
       </c>
       <c r="D94" t="n">
-        <v>18387</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>342.5806451612903</v>
+        <v>270</v>
       </c>
       <c r="B95" t="n">
-        <v>19032</v>
+        <v>15000</v>
       </c>
       <c r="C95" t="n">
-        <v>19032</v>
+        <v>15000</v>
       </c>
       <c r="D95" t="n">
-        <v>19032</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>354.1935483870968</v>
+        <v>272.9032258064516</v>
       </c>
       <c r="B96" t="n">
-        <v>19677</v>
+        <v>15161</v>
       </c>
       <c r="C96" t="n">
-        <v>19677</v>
+        <v>15161</v>
       </c>
       <c r="D96" t="n">
-        <v>19677</v>
+        <v>15161</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>365.8064516129032</v>
+        <v>275.8064516129032</v>
       </c>
       <c r="B97" t="n">
-        <v>20323</v>
+        <v>15323</v>
       </c>
       <c r="C97" t="n">
-        <v>20323</v>
+        <v>15323</v>
       </c>
       <c r="D97" t="n">
-        <v>20323</v>
+        <v>15323</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>8.70967741935484</v>
+        <v>278.7096774193549</v>
       </c>
       <c r="B98" t="n">
-        <v>484</v>
+        <v>15484</v>
       </c>
       <c r="C98" t="n">
-        <v>484</v>
+        <v>15484</v>
       </c>
       <c r="D98" t="n">
-        <v>484</v>
+        <v>15484</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20.32258064516129</v>
+        <v>281.6129032258065</v>
       </c>
       <c r="B99" t="n">
-        <v>1129</v>
+        <v>15645</v>
       </c>
       <c r="C99" t="n">
-        <v>1129</v>
+        <v>15645</v>
       </c>
       <c r="D99" t="n">
-        <v>1129</v>
+        <v>15645</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>31.93548387096774</v>
+        <v>284.516129032258</v>
       </c>
       <c r="B100" t="n">
-        <v>1774</v>
+        <v>15806</v>
       </c>
       <c r="C100" t="n">
-        <v>1774</v>
+        <v>15806</v>
       </c>
       <c r="D100" t="n">
-        <v>1774</v>
+        <v>15806</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>43.54838709677419</v>
+        <v>287.4193548387097</v>
       </c>
       <c r="B101" t="n">
-        <v>2419</v>
+        <v>15968</v>
       </c>
       <c r="C101" t="n">
-        <v>2419</v>
+        <v>15968</v>
       </c>
       <c r="D101" t="n">
-        <v>2419</v>
+        <v>15968</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>55.16129032258065</v>
+        <v>290.3225806451613</v>
       </c>
       <c r="B102" t="n">
-        <v>3065</v>
+        <v>16129</v>
       </c>
       <c r="C102" t="n">
-        <v>3065</v>
+        <v>16129</v>
       </c>
       <c r="D102" t="n">
-        <v>3065</v>
+        <v>16129</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>66.7741935483871</v>
+        <v>293.2258064516129</v>
       </c>
       <c r="B103" t="n">
-        <v>3710</v>
+        <v>16290</v>
       </c>
       <c r="C103" t="n">
-        <v>3710</v>
+        <v>16290</v>
       </c>
       <c r="D103" t="n">
-        <v>3710</v>
+        <v>16290</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>78.38709677419355</v>
+        <v>296.1290322580645</v>
       </c>
       <c r="B104" t="n">
-        <v>4355</v>
+        <v>16452</v>
       </c>
       <c r="C104" t="n">
-        <v>4355</v>
+        <v>16452</v>
       </c>
       <c r="D104" t="n">
-        <v>4355</v>
+        <v>16452</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>90</v>
+        <v>299.0322580645162</v>
       </c>
       <c r="B105" t="n">
-        <v>5000</v>
+        <v>16613</v>
       </c>
       <c r="C105" t="n">
-        <v>5000</v>
+        <v>16613</v>
       </c>
       <c r="D105" t="n">
-        <v>5000</v>
+        <v>16613</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>101.6129032258064</v>
+        <v>301.9354838709677</v>
       </c>
       <c r="B106" t="n">
-        <v>5645</v>
+        <v>16774</v>
       </c>
       <c r="C106" t="n">
-        <v>5645</v>
+        <v>16774</v>
       </c>
       <c r="D106" t="n">
-        <v>5645</v>
+        <v>16774</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>113.2258064516129</v>
+        <v>304.8387096774194</v>
       </c>
       <c r="B107" t="n">
-        <v>6290</v>
+        <v>16935</v>
       </c>
       <c r="C107" t="n">
-        <v>6290</v>
+        <v>16935</v>
       </c>
       <c r="D107" t="n">
-        <v>6290</v>
+        <v>16935</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124.8387096774194</v>
+        <v>307.741935483871</v>
       </c>
       <c r="B108" t="n">
-        <v>6935</v>
+        <v>17097</v>
       </c>
       <c r="C108" t="n">
-        <v>6935</v>
+        <v>17097</v>
       </c>
       <c r="D108" t="n">
-        <v>6935</v>
+        <v>17097</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136.4516129032258</v>
+        <v>310.6451612903226</v>
       </c>
       <c r="B109" t="n">
-        <v>7581</v>
+        <v>17258</v>
       </c>
       <c r="C109" t="n">
-        <v>7581</v>
+        <v>17258</v>
       </c>
       <c r="D109" t="n">
-        <v>7581</v>
+        <v>17258</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>148.0645161290323</v>
+        <v>313.5483870967742</v>
       </c>
       <c r="B110" t="n">
-        <v>8226</v>
+        <v>17419</v>
       </c>
       <c r="C110" t="n">
-        <v>8226</v>
+        <v>17419</v>
       </c>
       <c r="D110" t="n">
-        <v>8226</v>
+        <v>17419</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>159.6774193548387</v>
+        <v>316.4516129032258</v>
       </c>
       <c r="B111" t="n">
-        <v>8871</v>
+        <v>17581</v>
       </c>
       <c r="C111" t="n">
-        <v>8871</v>
+        <v>17581</v>
       </c>
       <c r="D111" t="n">
-        <v>8871</v>
+        <v>17581</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>171.2903225806452</v>
+        <v>319.3548387096774</v>
       </c>
       <c r="B112" t="n">
-        <v>9516</v>
+        <v>17742</v>
       </c>
       <c r="C112" t="n">
-        <v>9516</v>
+        <v>17742</v>
       </c>
       <c r="D112" t="n">
-        <v>9516</v>
+        <v>17742</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>182.9032258064516</v>
+        <v>322.258064516129</v>
       </c>
       <c r="B113" t="n">
-        <v>10161</v>
+        <v>17903</v>
       </c>
       <c r="C113" t="n">
-        <v>10161</v>
+        <v>17903</v>
       </c>
       <c r="D113" t="n">
-        <v>10161</v>
+        <v>17903</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>194.5161290322581</v>
+        <v>325.1612903225807</v>
       </c>
       <c r="B114" t="n">
-        <v>10806</v>
+        <v>18065</v>
       </c>
       <c r="C114" t="n">
-        <v>10806</v>
+        <v>18065</v>
       </c>
       <c r="D114" t="n">
-        <v>10806</v>
+        <v>18065</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>206.1290322580645</v>
+        <v>328.0645161290323</v>
       </c>
       <c r="B115" t="n">
-        <v>11452</v>
+        <v>18226</v>
       </c>
       <c r="C115" t="n">
-        <v>11452</v>
+        <v>18226</v>
       </c>
       <c r="D115" t="n">
-        <v>11452</v>
+        <v>18226</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>217.741935483871</v>
+        <v>330.9677419354839</v>
       </c>
       <c r="B116" t="n">
-        <v>12097</v>
+        <v>18387</v>
       </c>
       <c r="C116" t="n">
-        <v>12097</v>
+        <v>18387</v>
       </c>
       <c r="D116" t="n">
-        <v>12097</v>
+        <v>18387</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>229.3548387096774</v>
+        <v>333.8709677419355</v>
       </c>
       <c r="B117" t="n">
-        <v>12742</v>
+        <v>18548</v>
       </c>
       <c r="C117" t="n">
-        <v>12742</v>
+        <v>18548</v>
       </c>
       <c r="D117" t="n">
-        <v>12742</v>
+        <v>18548</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>240.9677419354839</v>
+        <v>336.7741935483871</v>
       </c>
       <c r="B118" t="n">
-        <v>13387</v>
+        <v>18710</v>
       </c>
       <c r="C118" t="n">
-        <v>13387</v>
+        <v>18710</v>
       </c>
       <c r="D118" t="n">
-        <v>13387</v>
+        <v>18710</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>252.5806451612903</v>
+        <v>339.6774193548387</v>
       </c>
       <c r="B119" t="n">
-        <v>14032</v>
+        <v>18871</v>
       </c>
       <c r="C119" t="n">
-        <v>14032</v>
+        <v>18871</v>
       </c>
       <c r="D119" t="n">
-        <v>14032</v>
+        <v>18871</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>264.1935483870968</v>
+        <v>342.5806451612903</v>
       </c>
       <c r="B120" t="n">
-        <v>14677</v>
+        <v>19032</v>
       </c>
       <c r="C120" t="n">
-        <v>14677</v>
+        <v>19032</v>
       </c>
       <c r="D120" t="n">
-        <v>14677</v>
+        <v>19032</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>275.8064516129032</v>
+        <v>345.483870967742</v>
       </c>
       <c r="B121" t="n">
-        <v>15323</v>
+        <v>19194</v>
       </c>
       <c r="C121" t="n">
-        <v>15323</v>
+        <v>19194</v>
       </c>
       <c r="D121" t="n">
-        <v>15323</v>
+        <v>19194</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>287.4193548387097</v>
+        <v>348.3870967741935</v>
       </c>
       <c r="B122" t="n">
-        <v>15968</v>
+        <v>19355</v>
       </c>
       <c r="C122" t="n">
-        <v>15968</v>
+        <v>19355</v>
       </c>
       <c r="D122" t="n">
-        <v>15968</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>299.0322580645162</v>
+        <v>351.2903225806452</v>
       </c>
       <c r="B123" t="n">
-        <v>16613</v>
+        <v>19516</v>
       </c>
       <c r="C123" t="n">
-        <v>16613</v>
+        <v>19516</v>
       </c>
       <c r="D123" t="n">
-        <v>16613</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>310.6451612903226</v>
+        <v>354.1935483870968</v>
       </c>
       <c r="B124" t="n">
-        <v>17258</v>
+        <v>19677</v>
       </c>
       <c r="C124" t="n">
-        <v>17258</v>
+        <v>19677</v>
       </c>
       <c r="D124" t="n">
-        <v>17258</v>
+        <v>19677</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>322.258064516129</v>
+        <v>357.0967741935484</v>
       </c>
       <c r="B125" t="n">
-        <v>17903</v>
+        <v>19839</v>
       </c>
       <c r="C125" t="n">
-        <v>17903</v>
+        <v>19839</v>
       </c>
       <c r="D125" t="n">
-        <v>17903</v>
+        <v>19839</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>333.8709677419355</v>
+        <v>360</v>
       </c>
       <c r="B126" t="n">
-        <v>18548</v>
+        <v>20000</v>
       </c>
       <c r="C126" t="n">
-        <v>18548</v>
+        <v>20000</v>
       </c>
       <c r="D126" t="n">
-        <v>18548</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>345.483870967742</v>
+        <v>362.9032258064516</v>
       </c>
       <c r="B127" t="n">
-        <v>19194</v>
+        <v>20161</v>
       </c>
       <c r="C127" t="n">
-        <v>19194</v>
+        <v>20161</v>
       </c>
       <c r="D127" t="n">
-        <v>19194</v>
+        <v>20161</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>357.0967741935484</v>
+        <v>365.8064516129032</v>
       </c>
       <c r="B128" t="n">
-        <v>19839</v>
+        <v>20323</v>
       </c>
       <c r="C128" t="n">
-        <v>19839</v>
+        <v>20323</v>
       </c>
       <c r="D128" t="n">
-        <v>19839</v>
+        <v>20323</v>
       </c>
     </row>
     <row r="129">
@@ -5933,10 +5933,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="D2" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451613</v>
       </c>
     </row>
     <row r="3">
@@ -5944,13 +5944,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2258064516129</v>
+        <v>5.806451612903226</v>
       </c>
       <c r="D3" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451613</v>
       </c>
     </row>
     <row r="4">
@@ -5958,13 +5958,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.2258064516129</v>
+        <v>5.806451612903226</v>
       </c>
       <c r="C4" t="n">
-        <v>34.83870967741936</v>
+        <v>8.70967741935484</v>
       </c>
       <c r="D4" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451614</v>
       </c>
     </row>
     <row r="5">
@@ -5972,13 +5972,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.83870967741936</v>
+        <v>8.70967741935484</v>
       </c>
       <c r="C5" t="n">
-        <v>46.45161290322581</v>
+        <v>11.61290322580645</v>
       </c>
       <c r="D5" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="6">
@@ -5986,13 +5986,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.45161290322581</v>
+        <v>11.61290322580645</v>
       </c>
       <c r="C6" t="n">
-        <v>58.06451612903226</v>
+        <v>14.51612903225806</v>
       </c>
       <c r="D6" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="7">
@@ -6000,13 +6000,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.06451612903226</v>
+        <v>14.51612903225806</v>
       </c>
       <c r="C7" t="n">
-        <v>69.67741935483872</v>
+        <v>17.41935483870968</v>
       </c>
       <c r="D7" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="8">
@@ -6014,13 +6014,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69.67741935483872</v>
+        <v>17.41935483870968</v>
       </c>
       <c r="C8" t="n">
-        <v>81.29032258064517</v>
+        <v>20.32258064516129</v>
       </c>
       <c r="D8" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="9">
@@ -6028,13 +6028,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81.29032258064517</v>
+        <v>20.32258064516129</v>
       </c>
       <c r="C9" t="n">
-        <v>92.90322580645162</v>
+        <v>23.2258064516129</v>
       </c>
       <c r="D9" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="10">
@@ -6042,13 +6042,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>92.90322580645162</v>
+        <v>23.2258064516129</v>
       </c>
       <c r="C10" t="n">
-        <v>104.5161290322581</v>
+        <v>26.12903225806452</v>
       </c>
       <c r="D10" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="11">
@@ -6056,13 +6056,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>104.5161290322581</v>
+        <v>26.12903225806452</v>
       </c>
       <c r="C11" t="n">
-        <v>116.1290322580645</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="D11" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451612</v>
       </c>
     </row>
     <row r="12">
@@ -6070,13 +6070,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>116.1290322580645</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="C12" t="n">
-        <v>127.741935483871</v>
+        <v>31.93548387096774</v>
       </c>
       <c r="D12" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="13">
@@ -6084,13 +6084,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>127.741935483871</v>
+        <v>31.93548387096774</v>
       </c>
       <c r="C13" t="n">
-        <v>139.3548387096774</v>
+        <v>34.83870967741936</v>
       </c>
       <c r="D13" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="14">
@@ -6098,13 +6098,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>139.3548387096774</v>
+        <v>34.83870967741936</v>
       </c>
       <c r="C14" t="n">
-        <v>150.9677419354839</v>
+        <v>37.74193548387097</v>
       </c>
       <c r="D14" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451609</v>
       </c>
     </row>
     <row r="15">
@@ -6112,13 +6112,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>150.9677419354839</v>
+        <v>37.74193548387097</v>
       </c>
       <c r="C15" t="n">
-        <v>162.5806451612903</v>
+        <v>40.64516129032258</v>
       </c>
       <c r="D15" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="16">
@@ -6126,13 +6126,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>162.5806451612903</v>
+        <v>40.64516129032258</v>
       </c>
       <c r="C16" t="n">
-        <v>174.1935483870968</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="D16" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451609</v>
       </c>
     </row>
     <row r="17">
@@ -6140,13 +6140,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>174.1935483870968</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="C17" t="n">
-        <v>185.8064516129032</v>
+        <v>46.45161290322581</v>
       </c>
       <c r="D17" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="18">
@@ -6154,13 +6154,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>185.8064516129032</v>
+        <v>46.45161290322581</v>
       </c>
       <c r="C18" t="n">
-        <v>197.4193548387097</v>
+        <v>49.35483870967742</v>
       </c>
       <c r="D18" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="19">
@@ -6168,13 +6168,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>197.4193548387097</v>
+        <v>49.35483870967742</v>
       </c>
       <c r="C19" t="n">
-        <v>209.0322580645161</v>
+        <v>52.25806451612903</v>
       </c>
       <c r="D19" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451609</v>
       </c>
     </row>
     <row r="20">
@@ -6182,13 +6182,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>209.0322580645161</v>
+        <v>52.25806451612903</v>
       </c>
       <c r="C20" t="n">
-        <v>220.6451612903226</v>
+        <v>55.16129032258065</v>
       </c>
       <c r="D20" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="21">
@@ -6196,13 +6196,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>220.6451612903226</v>
+        <v>55.16129032258065</v>
       </c>
       <c r="C21" t="n">
-        <v>232.258064516129</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="D21" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451609</v>
       </c>
     </row>
     <row r="22">
@@ -6210,13 +6210,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>232.258064516129</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="C22" t="n">
-        <v>243.8709677419355</v>
+        <v>60.96774193548387</v>
       </c>
       <c r="D22" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="23">
@@ -6224,13 +6224,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>243.8709677419355</v>
+        <v>60.96774193548387</v>
       </c>
       <c r="C23" t="n">
-        <v>255.483870967742</v>
+        <v>63.87096774193549</v>
       </c>
       <c r="D23" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="24">
@@ -6238,13 +6238,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>255.483870967742</v>
+        <v>63.87096774193549</v>
       </c>
       <c r="C24" t="n">
-        <v>267.0967741935484</v>
+        <v>66.7741935483871</v>
       </c>
       <c r="D24" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="25">
@@ -6252,13 +6252,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>267.0967741935484</v>
+        <v>66.7741935483871</v>
       </c>
       <c r="C25" t="n">
-        <v>278.7096774193549</v>
+        <v>69.67741935483872</v>
       </c>
       <c r="D25" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="26">
@@ -6266,13 +6266,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>278.7096774193549</v>
+        <v>69.67741935483872</v>
       </c>
       <c r="C26" t="n">
-        <v>290.3225806451613</v>
+        <v>72.58064516129032</v>
       </c>
       <c r="D26" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451601</v>
       </c>
     </row>
     <row r="27">
@@ -6280,13 +6280,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>290.3225806451613</v>
+        <v>72.58064516129032</v>
       </c>
       <c r="C27" t="n">
-        <v>301.9354838709677</v>
+        <v>75.48387096774194</v>
       </c>
       <c r="D27" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="28">
@@ -6294,13 +6294,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>301.9354838709677</v>
+        <v>75.48387096774194</v>
       </c>
       <c r="C28" t="n">
-        <v>313.5483870967742</v>
+        <v>78.38709677419355</v>
       </c>
       <c r="D28" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="29">
@@ -6308,13 +6308,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>313.5483870967742</v>
+        <v>78.38709677419355</v>
       </c>
       <c r="C29" t="n">
-        <v>325.1612903225807</v>
+        <v>81.29032258064517</v>
       </c>
       <c r="D29" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="30">
@@ -6322,13 +6322,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>325.1612903225807</v>
+        <v>81.29032258064517</v>
       </c>
       <c r="C30" t="n">
-        <v>336.7741935483871</v>
+        <v>84.19354838709678</v>
       </c>
       <c r="D30" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="31">
@@ -6336,13 +6336,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>336.7741935483871</v>
+        <v>84.19354838709678</v>
       </c>
       <c r="C31" t="n">
-        <v>348.3870967741935</v>
+        <v>87.09677419354838</v>
       </c>
       <c r="D31" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451601</v>
       </c>
     </row>
     <row r="32">
@@ -6350,13 +6350,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>348.3870967741935</v>
+        <v>87.09677419354838</v>
       </c>
       <c r="C32" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="D32" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="33">
@@ -6364,13 +6364,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="C33" t="n">
-        <v>2.903225806451613</v>
+        <v>92.90322580645162</v>
       </c>
       <c r="D33" t="n">
-        <v>-357.0967741935484</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="34">
@@ -6378,13 +6378,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2.903225806451613</v>
+        <v>92.90322580645162</v>
       </c>
       <c r="C34" t="n">
-        <v>14.51612903225806</v>
+        <v>95.80645161290323</v>
       </c>
       <c r="D34" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="35">
@@ -6392,13 +6392,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>14.51612903225806</v>
+        <v>95.80645161290323</v>
       </c>
       <c r="C35" t="n">
-        <v>26.12903225806452</v>
+        <v>98.70967741935485</v>
       </c>
       <c r="D35" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="36">
@@ -6406,13 +6406,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>26.12903225806452</v>
+        <v>98.70967741935485</v>
       </c>
       <c r="C36" t="n">
-        <v>37.74193548387097</v>
+        <v>101.6129032258064</v>
       </c>
       <c r="D36" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451601</v>
       </c>
     </row>
     <row r="37">
@@ -6420,13 +6420,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>37.74193548387097</v>
+        <v>101.6129032258064</v>
       </c>
       <c r="C37" t="n">
-        <v>49.35483870967742</v>
+        <v>104.5161290322581</v>
       </c>
       <c r="D37" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="38">
@@ -6434,13 +6434,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>49.35483870967742</v>
+        <v>104.5161290322581</v>
       </c>
       <c r="C38" t="n">
-        <v>60.96774193548387</v>
+        <v>107.4193548387097</v>
       </c>
       <c r="D38" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="39">
@@ -6448,13 +6448,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>60.96774193548387</v>
+        <v>107.4193548387097</v>
       </c>
       <c r="C39" t="n">
-        <v>72.58064516129032</v>
+        <v>110.3225806451613</v>
       </c>
       <c r="D39" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="40">
@@ -6462,13 +6462,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>72.58064516129032</v>
+        <v>110.3225806451613</v>
       </c>
       <c r="C40" t="n">
-        <v>84.19354838709678</v>
+        <v>113.2258064516129</v>
       </c>
       <c r="D40" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="41">
@@ -6476,13 +6476,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>84.19354838709678</v>
+        <v>113.2258064516129</v>
       </c>
       <c r="C41" t="n">
-        <v>95.80645161290323</v>
+        <v>116.1290322580645</v>
       </c>
       <c r="D41" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451601</v>
       </c>
     </row>
     <row r="42">
@@ -6490,13 +6490,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>95.80645161290323</v>
+        <v>116.1290322580645</v>
       </c>
       <c r="C42" t="n">
-        <v>107.4193548387097</v>
+        <v>119.0322580645161</v>
       </c>
       <c r="D42" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="43">
@@ -6504,13 +6504,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>107.4193548387097</v>
+        <v>119.0322580645161</v>
       </c>
       <c r="C43" t="n">
-        <v>119.0322580645161</v>
+        <v>121.9354838709677</v>
       </c>
       <c r="D43" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="44">
@@ -6518,13 +6518,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>119.0322580645161</v>
+        <v>121.9354838709677</v>
       </c>
       <c r="C44" t="n">
-        <v>130.6451612903226</v>
+        <v>124.8387096774194</v>
       </c>
       <c r="D44" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="45">
@@ -6532,13 +6532,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>130.6451612903226</v>
+        <v>124.8387096774194</v>
       </c>
       <c r="C45" t="n">
-        <v>142.258064516129</v>
+        <v>127.741935483871</v>
       </c>
       <c r="D45" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="46">
@@ -6546,13 +6546,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>142.258064516129</v>
+        <v>127.741935483871</v>
       </c>
       <c r="C46" t="n">
-        <v>153.8709677419355</v>
+        <v>130.6451612903226</v>
       </c>
       <c r="D46" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="47">
@@ -6560,13 +6560,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>153.8709677419355</v>
+        <v>130.6451612903226</v>
       </c>
       <c r="C47" t="n">
-        <v>165.483870967742</v>
+        <v>133.5483870967742</v>
       </c>
       <c r="D47" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="48">
@@ -6574,13 +6574,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>165.483870967742</v>
+        <v>133.5483870967742</v>
       </c>
       <c r="C48" t="n">
-        <v>177.0967741935484</v>
+        <v>136.4516129032258</v>
       </c>
       <c r="D48" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="49">
@@ -6588,13 +6588,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>177.0967741935484</v>
+        <v>136.4516129032258</v>
       </c>
       <c r="C49" t="n">
-        <v>188.7096774193548</v>
+        <v>139.3548387096774</v>
       </c>
       <c r="D49" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="50">
@@ -6602,13 +6602,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>188.7096774193548</v>
+        <v>139.3548387096774</v>
       </c>
       <c r="C50" t="n">
-        <v>200.3225806451613</v>
+        <v>142.258064516129</v>
       </c>
       <c r="D50" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="51">
@@ -6616,13 +6616,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>200.3225806451613</v>
+        <v>142.258064516129</v>
       </c>
       <c r="C51" t="n">
-        <v>211.9354838709677</v>
+        <v>145.1612903225806</v>
       </c>
       <c r="D51" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="52">
@@ -6630,13 +6630,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>211.9354838709677</v>
+        <v>145.1612903225806</v>
       </c>
       <c r="C52" t="n">
-        <v>223.5483870967742</v>
+        <v>148.0645161290323</v>
       </c>
       <c r="D52" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="53">
@@ -6644,13 +6644,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>223.5483870967742</v>
+        <v>148.0645161290323</v>
       </c>
       <c r="C53" t="n">
-        <v>235.1612903225806</v>
+        <v>150.9677419354839</v>
       </c>
       <c r="D53" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="54">
@@ -6658,13 +6658,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>235.1612903225806</v>
+        <v>150.9677419354839</v>
       </c>
       <c r="C54" t="n">
-        <v>246.7741935483871</v>
+        <v>153.8709677419355</v>
       </c>
       <c r="D54" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="55">
@@ -6672,13 +6672,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>246.7741935483871</v>
+        <v>153.8709677419355</v>
       </c>
       <c r="C55" t="n">
-        <v>258.3870967741935</v>
+        <v>156.7741935483871</v>
       </c>
       <c r="D55" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="56">
@@ -6686,13 +6686,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>258.3870967741935</v>
+        <v>156.7741935483871</v>
       </c>
       <c r="C56" t="n">
-        <v>270</v>
+        <v>159.6774193548387</v>
       </c>
       <c r="D56" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="57">
@@ -6700,13 +6700,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>270</v>
+        <v>159.6774193548387</v>
       </c>
       <c r="C57" t="n">
-        <v>281.6129032258065</v>
+        <v>162.5806451612903</v>
       </c>
       <c r="D57" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="58">
@@ -6714,13 +6714,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>281.6129032258065</v>
+        <v>162.5806451612903</v>
       </c>
       <c r="C58" t="n">
-        <v>293.2258064516129</v>
+        <v>165.483870967742</v>
       </c>
       <c r="D58" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="59">
@@ -6728,13 +6728,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>293.2258064516129</v>
+        <v>165.483870967742</v>
       </c>
       <c r="C59" t="n">
-        <v>304.8387096774194</v>
+        <v>168.3870967741936</v>
       </c>
       <c r="D59" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="60">
@@ -6742,13 +6742,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>304.8387096774194</v>
+        <v>168.3870967741936</v>
       </c>
       <c r="C60" t="n">
-        <v>316.4516129032258</v>
+        <v>171.2903225806452</v>
       </c>
       <c r="D60" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="61">
@@ -6756,13 +6756,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>316.4516129032258</v>
+        <v>171.2903225806452</v>
       </c>
       <c r="C61" t="n">
-        <v>328.0645161290323</v>
+        <v>174.1935483870968</v>
       </c>
       <c r="D61" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="62">
@@ -6770,13 +6770,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>328.0645161290323</v>
+        <v>174.1935483870968</v>
       </c>
       <c r="C62" t="n">
-        <v>339.6774193548387</v>
+        <v>177.0967741935484</v>
       </c>
       <c r="D62" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="63">
@@ -6784,13 +6784,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>339.6774193548387</v>
+        <v>177.0967741935484</v>
       </c>
       <c r="C63" t="n">
-        <v>351.2903225806452</v>
+        <v>180</v>
       </c>
       <c r="D63" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="64">
@@ -6798,13 +6798,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>351.2903225806452</v>
+        <v>180</v>
       </c>
       <c r="C64" t="n">
-        <v>362.9032258064516</v>
+        <v>182.9032258064516</v>
       </c>
       <c r="D64" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="65">
@@ -6812,13 +6812,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>362.9032258064516</v>
+        <v>182.9032258064516</v>
       </c>
       <c r="C65" t="n">
-        <v>5.806451612903226</v>
+        <v>185.8064516129032</v>
       </c>
       <c r="D65" t="n">
-        <v>-357.0967741935484</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="66">
@@ -6826,13 +6826,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>5.806451612903226</v>
+        <v>185.8064516129032</v>
       </c>
       <c r="C66" t="n">
-        <v>17.41935483870968</v>
+        <v>188.7096774193548</v>
       </c>
       <c r="D66" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="67">
@@ -6840,13 +6840,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>17.41935483870968</v>
+        <v>188.7096774193548</v>
       </c>
       <c r="C67" t="n">
-        <v>29.03225806451613</v>
+        <v>191.6129032258065</v>
       </c>
       <c r="D67" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="68">
@@ -6854,13 +6854,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>29.03225806451613</v>
+        <v>191.6129032258065</v>
       </c>
       <c r="C68" t="n">
-        <v>40.64516129032258</v>
+        <v>194.5161290322581</v>
       </c>
       <c r="D68" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="69">
@@ -6868,13 +6868,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>40.64516129032258</v>
+        <v>194.5161290322581</v>
       </c>
       <c r="C69" t="n">
-        <v>52.25806451612903</v>
+        <v>197.4193548387097</v>
       </c>
       <c r="D69" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="70">
@@ -6882,13 +6882,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>52.25806451612903</v>
+        <v>197.4193548387097</v>
       </c>
       <c r="C70" t="n">
-        <v>63.87096774193549</v>
+        <v>200.3225806451613</v>
       </c>
       <c r="D70" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="71">
@@ -6896,13 +6896,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>63.87096774193549</v>
+        <v>200.3225806451613</v>
       </c>
       <c r="C71" t="n">
-        <v>75.48387096774194</v>
+        <v>203.2258064516129</v>
       </c>
       <c r="D71" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="72">
@@ -6910,13 +6910,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>75.48387096774194</v>
+        <v>203.2258064516129</v>
       </c>
       <c r="C72" t="n">
-        <v>87.09677419354838</v>
+        <v>206.1290322580645</v>
       </c>
       <c r="D72" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="73">
@@ -6924,13 +6924,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>87.09677419354838</v>
+        <v>206.1290322580645</v>
       </c>
       <c r="C73" t="n">
-        <v>98.70967741935485</v>
+        <v>209.0322580645161</v>
       </c>
       <c r="D73" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="74">
@@ -6938,13 +6938,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>98.70967741935485</v>
+        <v>209.0322580645161</v>
       </c>
       <c r="C74" t="n">
-        <v>110.3225806451613</v>
+        <v>211.9354838709677</v>
       </c>
       <c r="D74" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="75">
@@ -6952,13 +6952,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>110.3225806451613</v>
+        <v>211.9354838709677</v>
       </c>
       <c r="C75" t="n">
-        <v>121.9354838709677</v>
+        <v>214.8387096774194</v>
       </c>
       <c r="D75" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="76">
@@ -6966,13 +6966,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>121.9354838709677</v>
+        <v>214.8387096774194</v>
       </c>
       <c r="C76" t="n">
-        <v>133.5483870967742</v>
+        <v>217.741935483871</v>
       </c>
       <c r="D76" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="77">
@@ -6980,13 +6980,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>133.5483870967742</v>
+        <v>217.741935483871</v>
       </c>
       <c r="C77" t="n">
-        <v>145.1612903225806</v>
+        <v>220.6451612903226</v>
       </c>
       <c r="D77" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="78">
@@ -6994,13 +6994,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>145.1612903225806</v>
+        <v>220.6451612903226</v>
       </c>
       <c r="C78" t="n">
-        <v>156.7741935483871</v>
+        <v>223.5483870967742</v>
       </c>
       <c r="D78" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="79">
@@ -7008,13 +7008,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>156.7741935483871</v>
+        <v>223.5483870967742</v>
       </c>
       <c r="C79" t="n">
-        <v>168.3870967741936</v>
+        <v>226.4516129032258</v>
       </c>
       <c r="D79" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="80">
@@ -7022,13 +7022,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>168.3870967741936</v>
+        <v>226.4516129032258</v>
       </c>
       <c r="C80" t="n">
-        <v>180</v>
+        <v>229.3548387096774</v>
       </c>
       <c r="D80" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="81">
@@ -7036,13 +7036,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>180</v>
+        <v>229.3548387096774</v>
       </c>
       <c r="C81" t="n">
-        <v>191.6129032258065</v>
+        <v>232.258064516129</v>
       </c>
       <c r="D81" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="82">
@@ -7050,13 +7050,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>191.6129032258065</v>
+        <v>232.258064516129</v>
       </c>
       <c r="C82" t="n">
-        <v>203.2258064516129</v>
+        <v>235.1612903225806</v>
       </c>
       <c r="D82" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="83">
@@ -7064,13 +7064,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>203.2258064516129</v>
+        <v>235.1612903225806</v>
       </c>
       <c r="C83" t="n">
-        <v>214.8387096774194</v>
+        <v>238.0645161290323</v>
       </c>
       <c r="D83" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="84">
@@ -7078,13 +7078,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>214.8387096774194</v>
+        <v>238.0645161290323</v>
       </c>
       <c r="C84" t="n">
-        <v>226.4516129032258</v>
+        <v>240.9677419354839</v>
       </c>
       <c r="D84" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="85">
@@ -7092,13 +7092,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>226.4516129032258</v>
+        <v>240.9677419354839</v>
       </c>
       <c r="C85" t="n">
-        <v>238.0645161290323</v>
+        <v>243.8709677419355</v>
       </c>
       <c r="D85" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="86">
@@ -7106,13 +7106,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>238.0645161290323</v>
+        <v>243.8709677419355</v>
       </c>
       <c r="C86" t="n">
-        <v>249.6774193548387</v>
+        <v>246.7741935483871</v>
       </c>
       <c r="D86" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="87">
@@ -7120,13 +7120,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
+        <v>246.7741935483871</v>
+      </c>
+      <c r="C87" t="n">
         <v>249.6774193548387</v>
       </c>
-      <c r="C87" t="n">
-        <v>261.2903225806452</v>
-      </c>
       <c r="D87" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="88">
@@ -7134,13 +7134,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>261.2903225806452</v>
+        <v>249.6774193548387</v>
       </c>
       <c r="C88" t="n">
-        <v>272.9032258064516</v>
+        <v>252.5806451612903</v>
       </c>
       <c r="D88" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="89">
@@ -7148,13 +7148,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>272.9032258064516</v>
+        <v>252.5806451612903</v>
       </c>
       <c r="C89" t="n">
-        <v>284.516129032258</v>
+        <v>255.483870967742</v>
       </c>
       <c r="D89" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451616</v>
       </c>
     </row>
     <row r="90">
@@ -7162,13 +7162,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>284.516129032258</v>
+        <v>255.483870967742</v>
       </c>
       <c r="C90" t="n">
-        <v>296.1290322580645</v>
+        <v>258.3870967741935</v>
       </c>
       <c r="D90" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="91">
@@ -7176,13 +7176,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>296.1290322580645</v>
+        <v>258.3870967741935</v>
       </c>
       <c r="C91" t="n">
-        <v>307.741935483871</v>
+        <v>261.2903225806452</v>
       </c>
       <c r="D91" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="92">
@@ -7190,13 +7190,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>307.741935483871</v>
+        <v>261.2903225806452</v>
       </c>
       <c r="C92" t="n">
-        <v>319.3548387096774</v>
+        <v>264.1935483870968</v>
       </c>
       <c r="D92" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="93">
@@ -7204,13 +7204,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>319.3548387096774</v>
+        <v>264.1935483870968</v>
       </c>
       <c r="C93" t="n">
-        <v>330.9677419354839</v>
+        <v>267.0967741935484</v>
       </c>
       <c r="D93" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="94">
@@ -7218,13 +7218,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>330.9677419354839</v>
+        <v>267.0967741935484</v>
       </c>
       <c r="C94" t="n">
-        <v>342.5806451612903</v>
+        <v>270</v>
       </c>
       <c r="D94" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="95">
@@ -7232,13 +7232,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>342.5806451612903</v>
+        <v>270</v>
       </c>
       <c r="C95" t="n">
-        <v>354.1935483870968</v>
+        <v>272.9032258064516</v>
       </c>
       <c r="D95" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="96">
@@ -7246,13 +7246,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>354.1935483870968</v>
+        <v>272.9032258064516</v>
       </c>
       <c r="C96" t="n">
-        <v>365.8064516129032</v>
+        <v>275.8064516129032</v>
       </c>
       <c r="D96" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="97">
@@ -7260,13 +7260,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>365.8064516129032</v>
+        <v>275.8064516129032</v>
       </c>
       <c r="C97" t="n">
-        <v>8.70967741935484</v>
+        <v>278.7096774193549</v>
       </c>
       <c r="D97" t="n">
-        <v>-357.0967741935484</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="98">
@@ -7274,13 +7274,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>8.70967741935484</v>
+        <v>278.7096774193549</v>
       </c>
       <c r="C98" t="n">
-        <v>20.32258064516129</v>
+        <v>281.6129032258065</v>
       </c>
       <c r="D98" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="99">
@@ -7288,13 +7288,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>20.32258064516129</v>
+        <v>281.6129032258065</v>
       </c>
       <c r="C99" t="n">
-        <v>31.93548387096774</v>
+        <v>284.516129032258</v>
       </c>
       <c r="D99" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="100">
@@ -7302,13 +7302,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>31.93548387096774</v>
+        <v>284.516129032258</v>
       </c>
       <c r="C100" t="n">
-        <v>43.54838709677419</v>
+        <v>287.4193548387097</v>
       </c>
       <c r="D100" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="101">
@@ -7316,13 +7316,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>43.54838709677419</v>
+        <v>287.4193548387097</v>
       </c>
       <c r="C101" t="n">
-        <v>55.16129032258065</v>
+        <v>290.3225806451613</v>
       </c>
       <c r="D101" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="102">
@@ -7330,13 +7330,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>55.16129032258065</v>
+        <v>290.3225806451613</v>
       </c>
       <c r="C102" t="n">
-        <v>66.7741935483871</v>
+        <v>293.2258064516129</v>
       </c>
       <c r="D102" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="103">
@@ -7344,13 +7344,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>66.7741935483871</v>
+        <v>293.2258064516129</v>
       </c>
       <c r="C103" t="n">
-        <v>78.38709677419355</v>
+        <v>296.1290322580645</v>
       </c>
       <c r="D103" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="104">
@@ -7358,13 +7358,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>78.38709677419355</v>
+        <v>296.1290322580645</v>
       </c>
       <c r="C104" t="n">
-        <v>90</v>
+        <v>299.0322580645162</v>
       </c>
       <c r="D104" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="105">
@@ -7372,13 +7372,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>90</v>
+        <v>299.0322580645162</v>
       </c>
       <c r="C105" t="n">
-        <v>101.6129032258064</v>
+        <v>301.9354838709677</v>
       </c>
       <c r="D105" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="106">
@@ -7386,13 +7386,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>101.6129032258064</v>
+        <v>301.9354838709677</v>
       </c>
       <c r="C106" t="n">
-        <v>113.2258064516129</v>
+        <v>304.8387096774194</v>
       </c>
       <c r="D106" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="107">
@@ -7400,13 +7400,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>113.2258064516129</v>
+        <v>304.8387096774194</v>
       </c>
       <c r="C107" t="n">
-        <v>124.8387096774194</v>
+        <v>307.741935483871</v>
       </c>
       <c r="D107" t="n">
-        <v>11.61290322580645</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="108">
@@ -7414,13 +7414,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>124.8387096774194</v>
+        <v>307.741935483871</v>
       </c>
       <c r="C108" t="n">
-        <v>136.4516129032258</v>
+        <v>310.6451612903226</v>
       </c>
       <c r="D108" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="109">
@@ -7428,13 +7428,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>136.4516129032258</v>
+        <v>310.6451612903226</v>
       </c>
       <c r="C109" t="n">
-        <v>148.0645161290323</v>
+        <v>313.5483870967742</v>
       </c>
       <c r="D109" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="110">
@@ -7442,13 +7442,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>148.0645161290323</v>
+        <v>313.5483870967742</v>
       </c>
       <c r="C110" t="n">
-        <v>159.6774193548387</v>
+        <v>316.4516129032258</v>
       </c>
       <c r="D110" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="111">
@@ -7456,13 +7456,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>159.6774193548387</v>
+        <v>316.4516129032258</v>
       </c>
       <c r="C111" t="n">
-        <v>171.2903225806452</v>
+        <v>319.3548387096774</v>
       </c>
       <c r="D111" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="112">
@@ -7470,13 +7470,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>171.2903225806452</v>
+        <v>319.3548387096774</v>
       </c>
       <c r="C112" t="n">
-        <v>182.9032258064516</v>
+        <v>322.258064516129</v>
       </c>
       <c r="D112" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="113">
@@ -7484,13 +7484,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>182.9032258064516</v>
+        <v>322.258064516129</v>
       </c>
       <c r="C113" t="n">
-        <v>194.5161290322581</v>
+        <v>325.1612903225807</v>
       </c>
       <c r="D113" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="114">
@@ -7498,13 +7498,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>194.5161290322581</v>
+        <v>325.1612903225807</v>
       </c>
       <c r="C114" t="n">
-        <v>206.1290322580645</v>
+        <v>328.0645161290323</v>
       </c>
       <c r="D114" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="115">
@@ -7512,13 +7512,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>206.1290322580645</v>
+        <v>328.0645161290323</v>
       </c>
       <c r="C115" t="n">
-        <v>217.741935483871</v>
+        <v>330.9677419354839</v>
       </c>
       <c r="D115" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="116">
@@ -7526,13 +7526,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>217.741935483871</v>
+        <v>330.9677419354839</v>
       </c>
       <c r="C116" t="n">
-        <v>229.3548387096774</v>
+        <v>333.8709677419355</v>
       </c>
       <c r="D116" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="117">
@@ -7540,13 +7540,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>229.3548387096774</v>
+        <v>333.8709677419355</v>
       </c>
       <c r="C117" t="n">
-        <v>240.9677419354839</v>
+        <v>336.7741935483871</v>
       </c>
       <c r="D117" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="118">
@@ -7554,13 +7554,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>240.9677419354839</v>
+        <v>336.7741935483871</v>
       </c>
       <c r="C118" t="n">
-        <v>252.5806451612903</v>
+        <v>339.6774193548387</v>
       </c>
       <c r="D118" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="119">
@@ -7568,13 +7568,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>252.5806451612903</v>
+        <v>339.6774193548387</v>
       </c>
       <c r="C119" t="n">
-        <v>264.1935483870968</v>
+        <v>342.5806451612903</v>
       </c>
       <c r="D119" t="n">
-        <v>11.61290322580643</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="120">
@@ -7582,13 +7582,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>264.1935483870968</v>
+        <v>342.5806451612903</v>
       </c>
       <c r="C120" t="n">
-        <v>275.8064516129032</v>
+        <v>345.483870967742</v>
       </c>
       <c r="D120" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="121">
@@ -7596,13 +7596,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>275.8064516129032</v>
+        <v>345.483870967742</v>
       </c>
       <c r="C121" t="n">
-        <v>287.4193548387097</v>
+        <v>348.3870967741935</v>
       </c>
       <c r="D121" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="122">
@@ -7610,13 +7610,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>287.4193548387097</v>
+        <v>348.3870967741935</v>
       </c>
       <c r="C122" t="n">
-        <v>299.0322580645162</v>
+        <v>351.2903225806452</v>
       </c>
       <c r="D122" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="123">
@@ -7624,13 +7624,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>299.0322580645162</v>
+        <v>351.2903225806452</v>
       </c>
       <c r="C123" t="n">
-        <v>310.6451612903226</v>
+        <v>354.1935483870968</v>
       </c>
       <c r="D123" t="n">
-        <v>11.61290322580641</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="124">
@@ -7638,13 +7638,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>310.6451612903226</v>
+        <v>354.1935483870968</v>
       </c>
       <c r="C124" t="n">
-        <v>322.258064516129</v>
+        <v>357.0967741935484</v>
       </c>
       <c r="D124" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="125">
@@ -7652,13 +7652,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>322.258064516129</v>
+        <v>357.0967741935484</v>
       </c>
       <c r="C125" t="n">
-        <v>333.8709677419355</v>
+        <v>360</v>
       </c>
       <c r="D125" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="126">
@@ -7666,13 +7666,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>333.8709677419355</v>
+        <v>360</v>
       </c>
       <c r="C126" t="n">
-        <v>345.483870967742</v>
+        <v>362.9032258064516</v>
       </c>
       <c r="D126" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
     <row r="127">
@@ -7680,13 +7680,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>345.483870967742</v>
+        <v>362.9032258064516</v>
       </c>
       <c r="C127" t="n">
-        <v>357.0967741935484</v>
+        <v>365.8064516129032</v>
       </c>
       <c r="D127" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451587</v>
       </c>
     </row>
     <row r="128">
@@ -7694,13 +7694,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>357.0967741935484</v>
+        <v>365.8064516129032</v>
       </c>
       <c r="C128" t="n">
         <v>368.7096774193549</v>
       </c>
       <c r="D128" t="n">
-        <v>11.61290322580646</v>
+        <v>2.903225806451644</v>
       </c>
     </row>
   </sheetData>
